--- a/data/agriculture/nagdi-reference-data.xlsx
+++ b/data/agriculture/nagdi-reference-data.xlsx
@@ -13,12 +13,13 @@
     <sheet name="InputCatalog" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="DiseaseCodes" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="VaccineCodes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ServiceProviders" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="PurposePolicies" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="SourceSubmissions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="ValidationIssues" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="DuplicateCandidates" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="CorrectionRequests" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Seasons" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ServiceProviders" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PurposePolicies" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="SourceSubmissions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="ValidationIssues" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="DuplicateCandidates" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="CorrectionRequests" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -795,6 +796,264 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>source_submission_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>source_office</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>submitted_by_role</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>submitted_on</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>source_file_label</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>record_count</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>validation_status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SUB-FARM-2026-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>District agriculture offices</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>registry_officer</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>farmer-register-march-2026.xlsx</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>accepted</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SUB-FARM-2026-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>West District Agriculture Office</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>registry_officer</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>west-farmer-corrections.xlsx</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>manual_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SUB-HOLD-2026-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Farm services offices</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>extension_supervisor</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>holdings-season-2026A.xlsx</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>accepted</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SUB-HOLD-2026-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>West Farm Services Office</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>extension_supervisor</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>west-holdings-conflict.xlsx</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>manual_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SUB-FARM-2024-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>South District Agriculture Office</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>registry_officer</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45306</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>south-register-legacy.xlsx</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>stale</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SUB-HOLD-2024-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>South Farm Services Office</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>extension_supervisor</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45306</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>south-holdings-legacy.xlsx</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>stale</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -935,7 +1194,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1030,7 +1289,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1116,7 +1375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1159,12 +1418,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sorghum</t>
+          <t>rice</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sorghum</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="C3" t="b">
@@ -1174,15 +1433,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>sorghum</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sorghum</t>
+        </is>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>teff</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Teff</t>
         </is>
       </c>
-      <c r="C4" t="b">
+      <c r="C5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1197,7 +1471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1245,6 +1519,26 @@
         </is>
       </c>
       <c r="D2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rice</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rice grain</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1259,11 +1553,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
@@ -1307,6 +1601,26 @@
         </is>
       </c>
       <c r="D2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>soil_moisture_extension</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Soil moisture extension package</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>visit</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1321,7 +1635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1369,6 +1683,26 @@
         </is>
       </c>
       <c r="D2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BRU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>cattle</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1464,63 +1798,59 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>provider_id</t>
+          <t>season</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>provider_name</t>
+          <t>season_name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>provider_type</t>
+          <t>starts_on</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>license_status</t>
+          <t>ends_on</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>valid_until</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SP-MARKET-01</t>
+          <t>2026A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Demo Licensed Market Analytics Provider</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>licensed_service_provider</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="n">
+          <t>2026 main agricultural season</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="D2" s="1" t="n">
         <v>46387</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1534,259 +1864,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>purpose_code</t>
+          <t>provider_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>public_service_code</t>
+          <t>provider_name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>lawful_basis_code</t>
+          <t>provider_type</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>allowed_recipient_types</t>
+          <t>license_status</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>allowed_disclosure_modes</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>retention_days</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>minimum_cell_count</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>geography_floor</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>suppression_policy</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>rare_category_suppression</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>onward_sharing_allowed</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>automated_decision_allowed</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>appeal_contact</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>audit_required</t>
+          <t>valid_until</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>climate-smart-input-support</t>
+          <t>SP-MARKET-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>climate_smart_input_voucher</t>
+          <t>Demo Licensed Market Analytics Provider</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>program_rule</t>
+          <t>licensed_service_provider</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>government_program,extension_authority</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>predicate,redacted_result</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>365</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>agri-appeals@example.gov</t>
-        </is>
-      </c>
-      <c r="N2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>livestock-movement-permit-review</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>livestock_movement_permit</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>permit_condition</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>animal_health_authority</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>predicate,redacted_result</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>730</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>animal-health-appeals@example.gov</t>
-        </is>
-      </c>
-      <c r="N3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>agricultural-market-sizing</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>agricultural_market_sizing</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>public_task</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>licensed_service_provider,planning_unit</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>90</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>district</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>suppress_cells_below_minimum_or_below_geography_floor</t>
-        </is>
-      </c>
-      <c r="J4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>nagdi-governance@example.gov</t>
-        </is>
-      </c>
-      <c r="N4" t="b">
-        <v>1</v>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>46387</v>
       </c>
     </row>
   </sheetData>
@@ -1800,251 +1937,301 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="41" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>source_submission_id</t>
+          <t>purpose_code</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>source_office</t>
+          <t>public_service_code</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>submitted_by_role</t>
+          <t>lawful_basis_code</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>submitted_on</t>
+          <t>published_by_authority</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>source_file_label</t>
+          <t>approval_status</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>record_count</t>
+          <t>allowed_recipient_types</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>validation_status</t>
+          <t>allowed_disclosure_modes</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>retention_days</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>minimum_cell_count</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>geography_floor</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>suppression_policy</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>rare_category_suppression</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>onward_sharing_allowed</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>automated_decision_allowed</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>appeal_contact</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>audit_required</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SUB-FARM-2026-01</t>
+          <t>climate-smart-input-support</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>District agriculture offices</t>
+          <t>climate_smart_input_voucher</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>registry_officer</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>46101</v>
+          <t>program_rule</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>National Agricultural Data Infrastructure Governance Body</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>farmer-register-march-2026.xlsx</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>7</v>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>government_program,extension_authority</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>accepted</t>
-        </is>
+          <t>predicate,redacted_result</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>365</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>agri-appeals@example.gov</t>
+        </is>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SUB-FARM-2026-02</t>
+          <t>livestock-movement-permit-review</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>West District Agriculture Office</t>
+          <t>livestock_movement_permit</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>registry_officer</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>46097</v>
+          <t>permit_condition</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>National Animal Health Authority</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>west-farmer-corrections.xlsx</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>animal_health_authority</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>manual_review</t>
-        </is>
+          <t>predicate,redacted_result</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>730</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>animal-health-appeals@example.gov</t>
+        </is>
+      </c>
+      <c r="P3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SUB-HOLD-2026-01</t>
+          <t>agricultural-market-sizing</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Farm services offices</t>
+          <t>agricultural_market_sizing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>extension_supervisor</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46104</v>
+          <t>public_task</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>National Agricultural Data Infrastructure Governance Body</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>holdings-season-2026A.xlsx</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>4</v>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>licensed_service_provider,planning_unit</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>accepted</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SUB-HOLD-2026-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>West Farm Services Office</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>extension_supervisor</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46097</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>west-holdings-conflict.xlsx</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>manual_review</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SUB-FARM-2024-02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>South District Agriculture Office</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>registry_officer</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45306</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>south-register-legacy.xlsx</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>stale</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SUB-HOLD-2024-02</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>South Farm Services Office</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>extension_supervisor</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45306</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>south-holdings-legacy.xlsx</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>stale</t>
-        </is>
+          <t>aggregate</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>90</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>suppress_cells_below_minimum_or_below_geography_floor</t>
+        </is>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>nagdi-governance@example.gov</t>
+        </is>
+      </c>
+      <c r="P4" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
